--- a/data/2026/41-vrancea/174744-focsani/budget_file.xlsx
+++ b/data/2026/41-vrancea/174744-focsani/budget_file.xlsx
@@ -3199,38 +3199,49 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>03.02</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Impozit teren extravilan</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="n">
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="I78" s="3" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="N78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
-      <c r="P78" s="3" t="n"/>
-      <c r="Q78" s="3" t="n"/>
-      <c r="R78" s="3" t="n"/>
-      <c r="S78" s="3" t="n"/>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="U78" s="4" t="inlineStr">
+        <is>
+          <t>03.02 total_2026: parent 310,00 != sum(children) 2,03 (1 children)</t>
         </is>
       </c>
     </row>
@@ -17422,38 +17433,49 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C439" s="2" t="inlineStr">
+      <c r="A439" s="6" t="inlineStr">
+        <is>
+          <t>31.02</t>
+        </is>
+      </c>
+      <c r="B439" s="6" t="n"/>
+      <c r="C439" s="6" t="inlineStr">
         <is>
           <t>(materiale dendrologice, ingrasaminte, unelte grădinărit, cosit gazon, tuns gard viu, toaletari copaci,costuri utilaje-carburanti, piese de schimb, utilități sere,etc) varsaminte la bugetul de stat aferent persoane cu handicap neincadrate</t>
         </is>
       </c>
-      <c r="E439" t="n">
+      <c r="D439" s="6" t="n"/>
+      <c r="E439" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" s="3" t="n"/>
-      <c r="H439" s="3" t="n">
+      <c r="F439" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G439" s="7" t="n"/>
+      <c r="H439" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I439" s="3" t="n"/>
-      <c r="J439" s="3" t="n"/>
-      <c r="K439" s="3" t="n"/>
-      <c r="L439" s="3" t="n"/>
-      <c r="M439" s="3" t="n"/>
-      <c r="N439" s="3" t="n"/>
-      <c r="O439" s="3" t="n"/>
-      <c r="P439" s="3" t="n"/>
-      <c r="Q439" s="3" t="n"/>
-      <c r="R439" s="3" t="n"/>
-      <c r="S439" s="3" t="n"/>
-      <c r="T439" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I439" s="7" t="n"/>
+      <c r="J439" s="7" t="n"/>
+      <c r="K439" s="7" t="n"/>
+      <c r="L439" s="7" t="n"/>
+      <c r="M439" s="7" t="n"/>
+      <c r="N439" s="7" t="n"/>
+      <c r="O439" s="7" t="n"/>
+      <c r="P439" s="7" t="n"/>
+      <c r="Q439" s="7" t="n"/>
+      <c r="R439" s="7" t="n"/>
+      <c r="S439" s="7" t="n"/>
+      <c r="T439" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="U439" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (13%): '(materiale dendrologice, ingrasaminte, u' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
@@ -17522,74 +17544,96 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C442" s="2" t="inlineStr">
+      <c r="A442" s="6" t="inlineStr">
+        <is>
+          <t>35.02</t>
+        </is>
+      </c>
+      <c r="B442" s="6" t="n"/>
+      <c r="C442" s="6" t="inlineStr">
         <is>
           <t>iluminat public</t>
         </is>
       </c>
-      <c r="E442" t="n">
+      <c r="D442" s="6" t="n"/>
+      <c r="E442" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" s="3" t="n"/>
-      <c r="H442" s="3" t="n">
+      <c r="F442" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G442" s="7" t="n"/>
+      <c r="H442" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="I442" s="3" t="n"/>
-      <c r="J442" s="3" t="n"/>
-      <c r="K442" s="3" t="n"/>
-      <c r="L442" s="3" t="n"/>
-      <c r="M442" s="3" t="n"/>
-      <c r="N442" s="3" t="n"/>
-      <c r="O442" s="3" t="n"/>
-      <c r="P442" s="3" t="n"/>
-      <c r="Q442" s="3" t="n"/>
-      <c r="R442" s="3" t="n"/>
-      <c r="S442" s="3" t="n"/>
-      <c r="T442" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I442" s="7" t="n"/>
+      <c r="J442" s="7" t="n"/>
+      <c r="K442" s="7" t="n"/>
+      <c r="L442" s="7" t="n"/>
+      <c r="M442" s="7" t="n"/>
+      <c r="N442" s="7" t="n"/>
+      <c r="O442" s="7" t="n"/>
+      <c r="P442" s="7" t="n"/>
+      <c r="Q442" s="7" t="n"/>
+      <c r="R442" s="7" t="n"/>
+      <c r="S442" s="7" t="n"/>
+      <c r="T442" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="U442" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (34%): 'iluminat public' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C443" s="2" t="inlineStr">
+      <c r="A443" s="6" t="inlineStr">
+        <is>
+          <t>35.02</t>
+        </is>
+      </c>
+      <c r="B443" s="6" t="n"/>
+      <c r="C443" s="6" t="inlineStr">
         <is>
           <t>materiale intretinere iluminat</t>
         </is>
       </c>
-      <c r="E443" t="n">
+      <c r="D443" s="6" t="n"/>
+      <c r="E443" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" s="3" t="n"/>
-      <c r="H443" s="3" t="n">
+      <c r="F443" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G443" s="7" t="n"/>
+      <c r="H443" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="I443" s="3" t="n"/>
-      <c r="J443" s="3" t="n"/>
-      <c r="K443" s="3" t="n"/>
-      <c r="L443" s="3" t="n"/>
-      <c r="M443" s="3" t="n"/>
-      <c r="N443" s="3" t="n"/>
-      <c r="O443" s="3" t="n"/>
-      <c r="P443" s="3" t="n"/>
-      <c r="Q443" s="3" t="n"/>
-      <c r="R443" s="3" t="n"/>
-      <c r="S443" s="3" t="n"/>
-      <c r="T443" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I443" s="7" t="n"/>
+      <c r="J443" s="7" t="n"/>
+      <c r="K443" s="7" t="n"/>
+      <c r="L443" s="7" t="n"/>
+      <c r="M443" s="7" t="n"/>
+      <c r="N443" s="7" t="n"/>
+      <c r="O443" s="7" t="n"/>
+      <c r="P443" s="7" t="n"/>
+      <c r="Q443" s="7" t="n"/>
+      <c r="R443" s="7" t="n"/>
+      <c r="S443" s="7" t="n"/>
+      <c r="T443" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="U443" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (35%): 'materiale intretinere iluminat' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28325,7 +28369,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>03.02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -28335,7 +28379,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 16.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 2 rows for 03.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28351,11 +28395,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -28365,7 +28409,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 35.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 4 rows for 16.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28429,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -28395,7 +28439,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 3 rows for 35.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28415,7 +28459,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -28425,7 +28469,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 4 rows for 11.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28441,11 +28485,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -28455,7 +28499,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 3 rows for 42.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28471,11 +28515,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -28485,7 +28529,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 2 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28505,7 +28549,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -28515,7 +28559,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28531,11 +28575,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -28545,7 +28589,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>LLM re-read 3 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28557,15 +28601,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p5: 0 cells recovered</t>
+          <t>LLM re-read 2 rows for 74.02 total_2026: still inconsistent — UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -28581,11 +28635,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p6: 1 cells recovered</t>
+          <t>unparseable-cell pass p5: 0 cells recovered</t>
         </is>
       </c>
     </row>
@@ -28601,11 +28655,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p15: 0 cells recovered</t>
+          <t>unparseable-cell pass p6: 1 cells recovered</t>
         </is>
       </c>
     </row>
@@ -28621,41 +28675,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p24: 8 cells recovered</t>
+          <t>unparseable-cell pass p15: 0 cells recovered</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>16.02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
+        <v>24</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.02 total_2026: parent 12,59 != sum(children) 90,51 (3 children)</t>
+          <t>unparseable-cell pass p24: 8 cells recovered</t>
         </is>
       </c>
     </row>
@@ -28671,11 +28715,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>03.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -28685,7 +28729,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.02 total_2026: parent 4,09 != sum(children) 967,12 (2 children)</t>
+          <t>03.02 total_2026: parent 310,00 != sum(children) 2,03 (1 children)</t>
         </is>
       </c>
     </row>
@@ -28701,11 +28745,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -28715,7 +28759,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.02 total_2026: parent 69,26 != sum(children) 169,16 (3 children)</t>
+          <t>16.02 total_2026: parent 12,59 != sum(children) 90,51 (3 children)</t>
         </is>
       </c>
     </row>
@@ -28735,7 +28779,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -28745,19 +28789,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42.02 total_2026: parent 11,75 != sum(children) 261,50 (2 children)</t>
+          <t>35.02 total_2026: parent 4,09 != sum(children) 967,12 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -28765,24 +28809,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (55%): 'SUBVENTII PENTRU INVESTITII' vs 'Subventii de la bugetul de stat'</t>
+          <t>11.02 total_2026: parent 69,26 != sum(children) 169,16 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -28790,12 +28839,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.02.69</t>
+          <t>42.02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2014-202' vs 'Subvenţii de la bugetul de stat către bu'</t>
+          <t>42.02 total_2026: parent 11,75 != sum(children) 261,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -28815,12 +28869,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.02.93</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (51%): 'Sume BS cofinantare proiecte UE 2021-202' vs 'Subvenţii de la bugetul de stat necesare'</t>
+          <t>name mismatch vs nomenclator (55%): 'SUBVENTII PENTRU INVESTITII' vs 'Subventii de la bugetul de stat'</t>
         </is>
       </c>
     </row>
@@ -28840,12 +28894,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.02.65</t>
+          <t>42.02.69</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Finanţarea Programului Naţional de Dezvo'</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2014-202' vs 'Subvenţii de la bugetul de stat către bu'</t>
         </is>
       </c>
     </row>
@@ -28865,12 +28919,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>42.02.93</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'SUME DE PRIMIT DE LA UE 2021-2027' vs 'Sume primite de la UE/alti donatori în c'</t>
+          <t>name mismatch vs nomenclator (51%): 'Sume BS cofinantare proiecte UE 2021-202' vs 'Subvenţii de la bugetul de stat necesare'</t>
         </is>
       </c>
     </row>
@@ -28886,41 +28940,41 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>42.02.65</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Finanţarea Programului Naţional de Dezvo'</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>45.02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>unparseable cell '2,115 1,000' in column total_2026</t>
+          <t>name mismatch vs nomenclator (50%): 'SUME DE PRIMIT DE LA UE 2021-2027' vs 'Sume primite de la UE/alti donatori în c'</t>
         </is>
       </c>
     </row>
@@ -28940,49 +28994,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>54.02.07</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (43%): '*Fond de rezerva bugetara *Fond pt.garan' vs 'Fond pentru garantarea împrumuturilor ex'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>55.02</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
+          <t>unparseable cell '2,115 1,000' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -28990,17 +29044,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>54.02.07</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 9,99 != sum(children) 180,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (43%): '*Fond de rezerva bugetara *Fond pt.garan' vs 'Fond pentru garantarea împrumuturilor ex'</t>
         </is>
       </c>
     </row>
@@ -29020,24 +29069,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (25%): 'Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -29045,12 +29094,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>61.02.05</t>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (52%): '*Protectia civila' vs 'Protectie civila si protectia contra inc'</t>
+          <t>61.02 total_2026: parent 9,99 != sum(children) 180,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -29075,37 +29129,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>61.02.05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 11,99 != sum(children) 11,96 (1 children)</t>
+          <t>name mismatch vs nomenclator (52%): '*Protectia civila' vs 'Protectie civila si protectia contra inc'</t>
         </is>
       </c>
     </row>
@@ -29121,7 +29170,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -29137,12 +29186,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -29150,12 +29199,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>66.02 total_2026: parent 11,99 != sum(children) 11,96 (1 children)</t>
         </is>
       </c>
     </row>
@@ -29187,12 +29241,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -29200,17 +29254,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 70,32 != sum(children) 34,32 (2 children)</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -29235,19 +29284,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -29255,7 +29304,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>70.02.10</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -29265,7 +29314,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>68.02 total_2026: parent 70,32 != sum(children) 34,32 (2 children)</t>
         </is>
       </c>
     </row>
@@ -29290,27 +29339,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>70.02.10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -29320,7 +29369,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 15,78 != sum(children) 450,00 (1 children)</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
@@ -29336,7 +29385,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -29352,12 +29401,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -29365,12 +29414,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'operatiuni financiare' vs 'TITLUL XX RAMBURSARI DE CREDITE'</t>
+          <t>74.02 total_2026: parent 15,78 != sum(children) 450,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -29395,7 +29449,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29415,12 +29469,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
+          <t>name mismatch vs nomenclator (38%): 'operatiuni financiare' vs 'TITLUL XX RAMBURSARI DE CREDITE'</t>
         </is>
       </c>
     </row>
@@ -29477,100 +29531,100 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>7</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>71</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>unparseable cell 'VENITURI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>est2027</t>
+        <v>7</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>72</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>unparseable cell 'Venituri operationale' in column est2027</t>
+          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>20</t>
+        <v>8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'proiecte Consiliul Local al Tinerilor' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>unparseable cell 'VENITURI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>80.02</t>
+        <v>8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Cap 80.02 Alte servicii economice genera' vs 'Împrumuturi pentru persoane cu statut de'</t>
+          <t>unparseable cell 'Venituri operationale' in column est2027</t>
         </is>
       </c>
     </row>
@@ -29586,16 +29640,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'investitii' vs 'TITLUL VII ALTE TRANSFERURI'</t>
+          <t>name mismatch vs nomenclator (34%): 'proiecte Consiliul Local al Tinerilor' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -29611,16 +29665,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'alte drepturi sociale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (35%): 'Cap 80.02 Alte servicii economice genera' vs 'Împrumuturi pentru persoane cu statut de'</t>
         </is>
       </c>
     </row>
@@ -29640,37 +29694,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'varsaminte la bugetul de stat aferent pe' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (32%): 'investitii' vs 'TITLUL VII ALTE TRANSFERURI'</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>11</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>unparseable cell "000'6" in column total_2026</t>
+          <t>name mismatch vs nomenclator (33%): 'alte drepturi sociale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -29686,48 +29740,48 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'finantare complementara scoala' vs 'Reparatii curente'</t>
+          <t>name mismatch vs nomenclator (44%): 'varsaminte la bugetul de stat aferent pe' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>20.02</t>
+        <v>11</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'finantare complementara gradinita' vs 'Reparatii curente'</t>
+          <t>unparseable cell "000'6" in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -29736,16 +29790,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>duplicate of p14 with different values</t>
+          <t>name mismatch vs nomenclator (13%): '(materiale dendrologice, ingrasaminte, u' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
@@ -29761,16 +29815,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'finantare de baza' vs 'Locuinte, servicii si dezvoltare publica'</t>
+          <t>name mismatch vs nomenclator (34%): 'iluminat public' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
@@ -29786,73 +29840,73 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'gradinita finantare de baza' vs 'Taxe pe servicii specifice'</t>
+          <t>name mismatch vs nomenclator (35%): 'materiale intretinere iluminat' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>15</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>14</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20.02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>unparseable cell '1,042.00 642.00' in column total</t>
+          <t>name mismatch vs nomenclator (38%): 'finantare complementara scoala' vs 'Reparatii curente'</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>14</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>20.02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>unparseable cell '1,195.00 854.00' in column total</t>
+          <t>name mismatch vs nomenclator (44%): 'finantare complementara gradinita' vs 'Reparatii curente'</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -29861,66 +29915,66 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'finantare complementara' vs 'Actiuni generale economice, comerciale s'</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>15</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>total</t>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>unparseable cell '1,009.00 469.00' in column total</t>
+          <t>name mismatch vs nomenclator (32%): 'finantare de baza' vs 'Locuinte, servicii si dezvoltare publica'</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>15</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>total</t>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>unparseable cell '826.00 761.00' in column total</t>
+          <t>name mismatch vs nomenclator (34%): 'gradinita finantare de baza' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
@@ -29936,16 +29990,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>unparseable cell '一' in column total_2026</t>
+          <t>unparseable cell '1,042.00 642.00' in column total</t>
         </is>
       </c>
     </row>
@@ -29961,41 +30015,41 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>unparseable cell 'A' in column total_2026</t>
+          <t>unparseable cell '1,195.00 854.00' in column total</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>15</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>unparseable cell 'B' in column total_2026</t>
+          <t>name mismatch vs nomenclator (36%): 'finantare complementara' vs 'Actiuni generale economice, comerciale s'</t>
         </is>
       </c>
     </row>
@@ -30011,16 +30065,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>unparseable cell 'II' in column total_2026</t>
+          <t>unparseable cell '1,009.00 469.00' in column total</t>
         </is>
       </c>
     </row>
@@ -30036,16 +30090,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅢII' in column total_2026</t>
+          <t>unparseable cell '826.00 761.00' in column total</t>
         </is>
       </c>
     </row>
@@ -30070,7 +30124,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>unparseable cell 'a' in column total_2026</t>
+          <t>unparseable cell '一' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30095,57 +30149,57 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>unparseable cell 'b' in column total_2026</t>
+          <t>unparseable cell 'A' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>51.02.07</t>
+        <v>17</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'AUTORITĂTI PUBLICE' vs 'Finanţarea studiilor de fezabilitate afe'</t>
+          <t>unparseable cell 'B' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>19</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>56</t>
+        <v>17</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (16%): '-r a t a n 1 2027' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
+          <t>unparseable cell 'II' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30155,47 +30209,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>19</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>60</t>
+        <v>17</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>unparseable cell 'ⅢII' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>19</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>70.02.07</t>
+        <v>17</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'LOCUINTE ŞI DEZVOLTARE PUBLICÃ, LOCUINTE' vs 'Alimantare cu gaze naturale in localitat'</t>
+          <t>unparseable cell 'a' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30205,29 +30259,29 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>19</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>56</t>
+        <v>17</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>unparseable cell 'b' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -30240,19 +30294,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>51.02.07</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'AUTORITĂTI PUBLICE' vs 'Finanţarea studiilor de fezabilitate afe'</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -30265,12 +30319,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>name mismatch vs nomenclator (16%): '-r a t a n 1 2027' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
         </is>
       </c>
     </row>
@@ -30290,7 +30344,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -30311,23 +30365,23 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>70.02.07</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>name mismatch vs nomenclator (46%): 'LOCUINTE ŞI DEZVOLTARE PUBLICÃ, LOCUINTE' vs 'Alimantare cu gaze naturale in localitat'</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -30336,16 +30390,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (43%): 'Sistem de avertizare audio-video si pano' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -30361,46 +30415,41 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -30410,34 +30459,34 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>24</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>19</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>unparseable cell 'IⅡI' in column total_2026</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -30445,17 +30494,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>24.02</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -30475,19 +30519,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+          <t>name mismatch vs nomenclator (43%): 'Sistem de avertizare audio-video si pano' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -30500,12 +30544,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'GRADINITA NR.18' vs 'Venituri din proprietate'</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -30525,7 +30569,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -30542,37 +30586,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>24</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V6_repair</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -30580,12 +30624,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>24.02</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
@@ -30610,19 +30659,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Venituri din proprietate'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -30633,26 +30682,21 @@
           <t>30.02</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (46%): 'GRADINITA NR.18' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V6_repair</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -30663,16 +30707,21 @@
           <t>30.02</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Documentatie Refacere imprejmuire Gradin' vs 'Venituri din proprietate'</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -30690,14 +30739,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -30715,19 +30764,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -30738,31 +30787,31 @@
           <t>30.02</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>24</v>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>30.02</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -30770,32 +30819,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>24</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (35%): 'Documentatie Refacere imprejmuire Gradin' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -30805,64 +30854,69 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>24</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>24</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>24</v>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>30.02</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -30870,7 +30924,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
@@ -30895,7 +30949,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>unparseable cell 'IⅡI' in column total_2026</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30920,7 +30974,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>unparseable cell 'I' in column total_2026</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30977,50 +31031,50 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>24</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>10.02</t>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>24</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>10.02</t>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'LICEUL CU PROGRAM SPORTIV' vs 'Cheltuieli salariale in natura'</t>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -31030,44 +31084,39 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>24</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>10.02</t>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>unparseable cell 'I' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>24</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -31075,32 +31124,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>24</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>10.02</t>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -31125,14 +31174,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (54%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Cheltuieli salariale in natura'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -31150,19 +31199,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>name mismatch vs nomenclator (44%): 'LICEUL CU PROGRAM SPORTIV' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -31173,26 +31222,21 @@
           <t>10.02</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V6_repair</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -31203,9 +31247,14 @@
           <t>10.02</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Statie dedurizare apa' vs 'Cheltuieli salariale in natura'</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31286,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -31255,19 +31304,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>name mismatch vs nomenclator (54%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -31278,31 +31327,31 @@
           <t>10.02</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>info</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>24</v>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>10.02</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -31310,64 +31359,64 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>unparseable cell 'I' in column total_2026</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>24</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>unparseable cell 'II' in column total_2026</t>
+          <t>name mismatch vs nomenclator (39%): 'Statie dedurizare apa' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>24</v>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -31376,64 +31425,194 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Documentatie PUZ Amenajare cale de acces' vs 'Locuinte, servicii si dezvoltare publica'</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V6_repair</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>10.02</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Placa vibro-compactoare' vs 'Cheltuieli salariale in natura'</t>
+          <t>cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>24</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>unparseable cell 'I' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>24</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>unparseable cell 'II' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>24</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>V2_name</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>warning</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="C125" t="n">
         <v>30</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (36%): 'Documentatie PUZ Amenajare cale de acces' vs 'Locuinte, servicii si dezvoltare publica'</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>30</v>
+      </c>
+      <c r="D126" t="inlineStr">
         <is>
           <t>10.02</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (30%): 'Placa vibro-compactoare' vs 'Cheltuieli salariale in natura'</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>30</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>10.02</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
@@ -31486,7 +31665,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4">
@@ -31506,7 +31685,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="6">
@@ -31516,7 +31695,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -31526,7 +31705,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">

--- a/data/2026/41-vrancea/174744-focsani/budget_file.xlsx
+++ b/data/2026/41-vrancea/174744-focsani/budget_file.xlsx
@@ -561,12 +561,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>transferuri</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>inst_integral_venituri_proprii</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>transferuri</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -606,10 +606,10 @@
         <v>71.625</v>
       </c>
       <c r="R2" s="3" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>25.34</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>-17.05</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         <v>205.28</v>
       </c>
       <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="S3" s="3" t="n"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -764,10 +764,10 @@
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="S7" s="3" t="n"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -797,10 +797,10 @@
         <v>69.255</v>
       </c>
       <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="3" t="n"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -1109,10 +1109,10 @@
         <v>28.419</v>
       </c>
       <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="3" t="n"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -1358,10 +1358,10 @@
       <c r="P26" s="3" t="n"/>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>17.05</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-17.05</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         <v>71.625</v>
       </c>
       <c r="R29" s="3" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>25.34</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>-17.05</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
       <c r="Q35" s="3" t="n">
         <v>718</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="3" t="n"/>
+      <c r="S35" s="3" t="n">
         <v>7.77</v>
       </c>
-      <c r="S35" s="3" t="n"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -1710,10 +1710,10 @@
         <v>7.5</v>
       </c>
       <c r="R36" s="3" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="S36" s="3" t="n">
         <v>17.57</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>-17.05</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         <v>71.625</v>
       </c>
       <c r="R43" s="3" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="S43" s="3" t="n">
         <v>25.34</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>-17.05</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="R44" s="3" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="S44" s="3" t="n">
         <v>25.34</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>-17.05</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         <v>101.669</v>
       </c>
       <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n">
         <v>4.808</v>
       </c>
-      <c r="S45" s="3" t="n"/>
       <c r="T45" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -2067,10 +2067,10 @@
         <v>87.51900000000001</v>
       </c>
       <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n">
         <v>20.492</v>
       </c>
-      <c r="S46" s="3" t="n"/>
       <c r="T46" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -2205,10 +2205,10 @@
         <v>17.05</v>
       </c>
       <c r="Q50" s="3" t="n"/>
-      <c r="R50" s="3" t="n"/>
-      <c r="S50" s="3" t="n">
+      <c r="R50" s="3" t="n">
         <v>-17.05</v>
       </c>
+      <c r="S50" s="3" t="n"/>
       <c r="T50" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -2309,10 +2309,10 @@
         <v>2.98</v>
       </c>
       <c r="Q53" s="3" t="n"/>
-      <c r="R53" s="3" t="n">
+      <c r="R53" s="3" t="n"/>
+      <c r="S53" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="S53" s="3" t="n"/>
       <c r="T53" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -10181,43 +10181,43 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>70.02.10</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="8" t="inlineStr">
         <is>
           <t>Locuinte, servicii si dezv.publica cheltuieli de personal</t>
         </is>
       </c>
-      <c r="E239" t="n">
+      <c r="D239" s="4" t="n"/>
+      <c r="E239" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" s="3" t="n"/>
-      <c r="H239" s="3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="I239" s="3" t="n"/>
-      <c r="J239" s="3" t="n"/>
-      <c r="K239" s="3" t="n"/>
-      <c r="L239" s="3" t="n"/>
-      <c r="M239" s="3" t="n"/>
-      <c r="N239" s="3" t="n"/>
-      <c r="O239" s="3" t="n"/>
-      <c r="P239" s="3" t="n"/>
-      <c r="Q239" s="3" t="n"/>
-      <c r="R239" s="3" t="n"/>
-      <c r="S239" s="3" t="n"/>
-      <c r="T239" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="F239" s="4" t="inlineStr"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
+      <c r="J239" s="5" t="n"/>
+      <c r="K239" s="5" t="n"/>
+      <c r="L239" s="5" t="n"/>
+      <c r="M239" s="5" t="n"/>
+      <c r="N239" s="5" t="n"/>
+      <c r="O239" s="5" t="n"/>
+      <c r="P239" s="5" t="n"/>
+      <c r="Q239" s="5" t="n"/>
+      <c r="R239" s="5" t="n"/>
+      <c r="S239" s="5" t="n"/>
+      <c r="T239" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="U239" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell '45,997 6,750' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -23994,7 +23994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24276,7 +24276,7 @@
     <row r="13">
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>II a Liceului cu program sportiv ⅡI Creșterea performanței energetice si lucrari conexe pentru cladirea internat I</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -24296,7 +24296,7 @@
     <row r="14">
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>a Liceului cu program sportiv ⅡI Creșterea performanței energetice si lucrari conexe pentru cladirea internat I</t>
+          <t>_Cresterea performantei energetice si lucrari auxiliare pentru Colegiul Tehnic Edmond Nicolau ⅡI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" s="3" t="n">
-        <v>6006</v>
+        <v>1000</v>
       </c>
       <c r="H14" s="3" t="n"/>
       <c r="I14" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="15">
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>_Cresterea performantei energetice si lucrari auxiliare pentru Colegiul Tehnic Edmond Nicolau ⅡI</t>
+          <t>I 1 67.02 CULTURĂ, RECREERE ŞI RELIGIE II I PRIMĂRIA MUNICIPIULUI FOCŞANI II</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" s="3" t="n">
-        <v>1000</v>
+        <v>50415.6</v>
       </c>
       <c r="H15" s="3" t="n"/>
       <c r="I15" t="inlineStr">
@@ -24334,17 +24334,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>I 1 67.02 CULTURĂ, RECREERE ŞI RELIGIE II I PRIMĂRIA MUNICIPIULUI FOCŞANI II</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="E16" t="n">
         <v>20</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" s="3" t="n">
-        <v>50415.6</v>
+        <v>10213.93</v>
       </c>
       <c r="H16" s="3" t="n"/>
       <c r="I16" t="inlineStr">
@@ -24354,13 +24350,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ⅡI</t>
+        </is>
+      </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" s="3" t="n">
-        <v>10213.93</v>
+        <v>500</v>
       </c>
       <c r="H17" s="3" t="n"/>
       <c r="I17" t="inlineStr">
@@ -24372,7 +24372,7 @@
     <row r="18">
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ⅡI</t>
+          <t>1 LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -24380,7 +24380,7 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" s="3" t="n">
-        <v>500</v>
+        <v>576.5700000000001</v>
       </c>
       <c r="H18" s="3" t="n"/>
       <c r="I18" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="19">
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1 LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
+          <t>II</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" s="3" t="n">
-        <v>576.5700000000001</v>
+        <v>1020</v>
       </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="20">
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>1 PRIMĂRIA MUNICIPIULUI FOCŞANI Reabilitarea, modernizarea și extinderea Sistemului de iluminat public - II nivelulul 1 de prioritate</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" s="3" t="n">
-        <v>1020</v>
+        <v>576.5700000000001</v>
       </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" t="inlineStr">
@@ -24432,7 +24432,7 @@
     <row r="21">
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1 PRIMĂRIA MUNICIPIULUI FOCŞANI Reabilitarea, modernizarea și extinderea Sistemului de iluminat public - II nivelulul 1 de prioritate</t>
+          <t>ⅡI</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -24440,7 +24440,7 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" s="3" t="n">
-        <v>576.5700000000001</v>
+        <v>1020</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" t="inlineStr">
@@ -24452,7 +24452,7 @@
     <row r="22">
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ⅡI</t>
+          <t>1 81.02 COMBUSTIBILI ŞI ENERGIE</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" s="3" t="n">
-        <v>1020</v>
+        <v>792.52</v>
       </c>
       <c r="H22" s="3" t="n"/>
       <c r="I22" t="inlineStr">
@@ -24472,7 +24472,7 @@
     <row r="23">
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1 81.02 COMBUSTIBILI ŞI ENERGIE</t>
+          <t>II</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>792.52</v>
+        <v>31547.86</v>
       </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" t="inlineStr">
@@ -24492,7 +24492,7 @@
     <row r="24">
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -24500,7 +24500,7 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" s="3" t="n">
-        <v>31547.86</v>
+        <v>792.52</v>
       </c>
       <c r="H24" s="3" t="n"/>
       <c r="I24" t="inlineStr">
@@ -24512,7 +24512,7 @@
     <row r="25">
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
+          <t>II</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" s="3" t="n">
-        <v>792.52</v>
+        <v>31547.86</v>
       </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" t="inlineStr">
@@ -24532,16 +24532,14 @@
     <row r="26">
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>CAPITOL/OBIECTIV</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" s="3" t="n">
-        <v>31547.86</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -24552,7 +24550,7 @@
     <row r="27">
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CAPITOL/OBIECTIV</t>
+          <t>_Reabilitarea sistemului de termoficare urbană la nivelul municipiului Focșani pentru perioada 2009-2028 în scopul conformării la legislația de mediu și</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -24570,7 +24568,7 @@
     <row r="28">
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>_Reabilitarea sistemului de termoficare urbană la nivelul municipiului Focșani pentru perioada 2009-2028 în scopul conformării la legislația de mediu și</t>
+          <t>creșterii eficienței energetice - etapa a Ill a</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -24588,7 +24586,7 @@
     <row r="29">
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>creșterii eficienței energetice - etapa a Ill a</t>
+          <t>TRANSPORTURI</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -24606,7 +24604,7 @@
     <row r="30">
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TRANSPORTURI</t>
+          <t>84.02 PRIMĂRIA MUNICIPIULUI FOCŞANI II _Dezvoltarea retelei de piste dedicate circulației bicicletelor, implementarea unui sistem de bike-sharing _Resistematizarea infrastructurii de transport la nivelul mun.Focșani în vederea creșterii atractivității și accesibilității deplasărilor cu transportul public, cu bicicleta și pietonale Optimizarea coridorului Nord-Sud prin realizarea retelei de terminale intermodale, cresterea accesibilitatii retelei de transport - Componenta 1 P.N.R.R.</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -24614,7 +24612,9 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="H30" s="3" t="n">
+        <v>84.02</v>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -24624,7 +24624,7 @@
     <row r="31">
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>84.02 PRIMĂRIA MUNICIPIULUI FOCŞANI II _Dezvoltarea retelei de piste dedicate circulației bicicletelor, implementarea unui sistem de bike-sharing _Resistematizarea infrastructurii de transport la nivelul mun.Focșani în vederea creșterii atractivității și accesibilității deplasărilor cu transportul public, cu bicicleta și pietonale Optimizarea coridorului Nord-Sud prin realizarea retelei de terminale intermodale, cresterea accesibilitatii retelei de transport - Componenta 1 P.N.R.R.</t>
+          <t>AUTORITĂTI EXECUTIVE PRIMĂRIA MUNICIPIULUI FOCŞANI Creșterea eficienței energetice a clădirii Primăriei Municipiului Focșani 65.02 îNVĂTĂMÂNT PRIMĂRIA MUNICIPIULUI FOCŞANI Renovarea energetica a cladirilor Scolii Gimnaziale Al.Vlahuta si Scolii Gimnaziale Nicolae lorga</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -24633,7 +24633,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="3" t="n">
-        <v>84.02</v>
+        <v>51.02</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
     <row r="32">
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>AUTORITĂTI EXECUTIVE PRIMĂRIA MUNICIPIULUI FOCŞANI Creșterea eficienței energetice a clădirii Primăriei Municipiului Focșani 65.02 îNVĂTĂMÂNT PRIMĂRIA MUNICIPIULUI FOCŞANI Renovarea energetica a cladirilor Scolii Gimnaziale Al.Vlahuta si Scolii Gimnaziale Nicolae lorga</t>
+          <t>CULTURĂ, RECREERE ŞI RELIGIE PRIMĂRIA MUNICIPIULUI FOCŞANI II Creșterea performanței energetice a Cinematografului Unirea</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -24653,7 +24653,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="n">
-        <v>51.02</v>
+        <v>67.02</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
     <row r="33">
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CULTURĂ, RECREERE ŞI RELIGIE PRIMĂRIA MUNICIPIULUI FOCŞANI II Creșterea performanței energetice a Cinematografului Unirea</t>
+          <t>ASIGURĂRI ŞI ASISTENTĂ SOCIALĂ II PRIMĂRIA MUNICIPIULUI FOCŞANI II Centru de zi de asistenta si recuperare pentru persoanele varstnice si unitate de ingrijire la domiciliu</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -24673,7 +24673,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n">
-        <v>67.02</v>
+        <v>68.02</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -24684,17 +24684,15 @@
     <row r="34">
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ASIGURĂRI ŞI ASISTENTĂ SOCIALĂ II PRIMĂRIA MUNICIPIULUI FOCŞANI II Centru de zi de asistenta si recuperare pentru persoanele varstnice si unitate de ingrijire la domiciliu</t>
+          <t>LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n">
-        <v>68.02</v>
-      </c>
+      <c r="H34" s="3" t="n"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -24704,7 +24702,7 @@
     <row r="35">
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -24722,7 +24720,7 @@
     <row r="36">
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
+          <t>Construirea de locuințe nZEB plus pentru tineri în mun. Focșani</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -24740,7 +24738,7 @@
     <row r="37">
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Construirea de locuințe nZEB plus pentru tineri în mun. Focșani</t>
+          <t>TRANSPORTURI</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -24758,7 +24756,7 @@
     <row r="38">
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>TRANSPORTURI</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -24776,7 +24774,7 @@
     <row r="39">
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
+          <t>_Achiziția de autobuze ecologice, stații de încărcare și sisteme asociate</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -24794,7 +24792,7 @@
     <row r="40">
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>_Achiziția de autobuze ecologice, stații de încărcare și sisteme asociate</t>
+          <t>_Achiziția de autobuze ecologice, stații de încărcare și sisteme asociate etapa a Il a</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -24812,7 +24810,7 @@
     <row r="41">
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>_Achiziția de autobuze ecologice, stații de încărcare și sisteme asociate etapa a Il a</t>
+          <t>Extinderea sistemului de management integrat al traficului si prioritizarea</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -24830,7 +24828,7 @@
     <row r="42">
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Extinderea sistemului de management integrat al traficului si prioritizarea</t>
+          <t>transportului public, inclusiv măsuri de monitorizare a parametrilor de mediu</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -24848,7 +24846,7 @@
     <row r="43">
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>transportului public, inclusiv măsuri de monitorizare a parametrilor de mediu</t>
+          <t>și reducerea poluării</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -24866,7 +24864,7 @@
     <row r="44">
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>și reducerea poluării</t>
+          <t>Extinderea sistemului de management integrat al traficului si prioritizarea transportului public, inclusiv măsuri de monitorizare a parametrilor de mediu</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -24884,7 +24882,7 @@
     <row r="45">
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Extinderea sistemului de management integrat al traficului si prioritizarea transportului public, inclusiv măsuri de monitorizare a parametrilor de mediu</t>
+          <t>și reducerea poluării etapa a Il a</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -24902,7 +24900,7 @@
     <row r="46">
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>și reducerea poluării etapa a Il a</t>
+          <t>FONDUL DE MODERNIZARE</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -24920,7 +24918,7 @@
     <row r="47">
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>FONDUL DE MODERNIZARE</t>
+          <t>LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -24938,7 +24936,7 @@
     <row r="48">
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -24956,7 +24954,7 @@
     <row r="49">
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
+          <t>Caae  e ies s cue e oie i egie</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -24974,7 +24972,7 @@
     <row r="50">
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Caae  e ies s cue e oie i egie</t>
+          <t>pentru consum propriu al UAT Municipiul Focsani</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -24992,7 +24990,7 @@
     <row r="51">
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>pentru consum propriu al UAT Municipiul Focsani</t>
+          <t>B. CHELTUIELI DE CAPITAL - TOTAL</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -25010,7 +25008,7 @@
     <row r="52">
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>B. CHELTUIELI DE CAPITAL - TOTAL</t>
+          <t>Autoritati executive</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -25028,7 +25026,7 @@
     <row r="53">
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Autoritati executive</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -25046,7 +25044,7 @@
     <row r="54">
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
+          <t>A ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -25064,7 +25062,7 @@
     <row r="55">
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>A ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Selfpoint-infochiosk (2 buc)</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -25082,7 +25080,7 @@
     <row r="56">
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Selfpoint-infochiosk (2 buc)</t>
+          <t>Modul automatizari popriri</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -25100,11 +25098,11 @@
     <row r="57">
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Modul automatizari popriri</t>
+          <t>Modul prescriptabilitate</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" s="3" t="n"/>
@@ -25118,7 +25116,7 @@
     <row r="58">
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Modul prescriptabilitate</t>
+          <t>Centrala termica 35 kW cu montaj si punere in functiune</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -25136,7 +25134,7 @@
     <row r="59">
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Centrala termica 35 kW cu montaj si punere in functiune</t>
+          <t>Alte servicii publice generale DIRECTIA DE DEZVOLTARE SERVICII PUBLICE Amenajare Cimitir Sudic Valcele etapa a Il a SERVICIUL PUBLIC LOCAL DE EVIDENTA A PERSOANELOR Calculator (2 buc) Laptop</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -25144,7 +25142,9 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>54.02</v>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -25154,7 +25154,7 @@
     <row r="60">
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale DIRECTIA DE DEZVOLTARE SERVICII PUBLICE Amenajare Cimitir Sudic Valcele etapa a Il a SERVICIUL PUBLIC LOCAL DE EVIDENTA A PERSOANELOR Calculator (2 buc) Laptop</t>
+          <t>Ordine publică si siguranța națională PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Modul informatic - Politia Locala</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -25163,7 +25163,7 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" s="3" t="n"/>
       <c r="H60" s="3" t="n">
-        <v>54.02</v>
+        <v>61.02</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
     <row r="61">
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ordine publică si siguranța națională PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Modul informatic - Politia Locala</t>
+          <t>îNVĂTĂMÂNT COLEGIUL NATIONAL AL.I.CUZA ALTE CHELTUIELI DE INVESTITII DALI -Demolare corp B Colegiul National Al.I.Cuza Rampa acces persoane cu dizabilitati corp A COLEGIUL TEHNIC AUTO TRAIAN VUIA A ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -25183,7 +25183,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" s="3" t="n"/>
       <c r="H61" s="3" t="n">
-        <v>61.02</v>
+        <v>65.02</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -25192,102 +25192,98 @@
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>îNVĂTĂMÂNT COLEGIUL NATIONAL AL.I.CUZA ALTE CHELTUIELI DE INVESTITII DALI -Demolare corp B Colegiul National Al.I.Cuza Rampa acces persoane cu dizabilitati corp A COLEGIUL TEHNIC AUTO TRAIAN VUIA A ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>23</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="inlineStr"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>12.02</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="inlineStr"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n">
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Sistem de avertizare audio-video si panouri luminoase</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026; name mismatch vs nomenclator (43%): 'Sistem de avertizare audio-video si pano' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p24 with different values</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe generale pe bunuri'</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Sistem de avertizare audio-video si panouri luminoase</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (43%): 'Sistem de avertizare audio-video si pano' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p24 with different values; cell re-read from image (unverified transcription)</t>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="C65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Harta tactila pentru nevazatori</t>
+        </is>
+      </c>
       <c r="E65" t="n">
         <v>24</v>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="G65" s="3" t="n"/>
       <c r="H65" s="3" t="n"/>
       <c r="I65" t="inlineStr">
         <is>
@@ -25296,123 +25292,139 @@
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Harta tactila pentru nevazatori</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
+      <c r="A66" s="4" t="n"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="8" t="inlineStr"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="8" t="inlineStr"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>24.02</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Platforma pentru accesul persoanelor cu dizabilitati</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
         <v>24</v>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>unparseable cell 'IⅡI' in column total_2026</t>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>24.02</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Platforma pentru accesul persoanelor cu dizabilitati</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="8" t="inlineStr"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>24.02</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="E69" t="n">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>30.02</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="inlineStr"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" s="3" t="n">
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>30.02</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n"/>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>GRADINITA NR.18</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="inlineStr"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'II' in column total_2026; name mismatch vs nomenclator (46%): 'GRADINITA NR.18' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -25423,11 +25435,7 @@
         </is>
       </c>
       <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>GRADINITA NR.18</t>
-        </is>
-      </c>
+      <c r="C71" s="6" t="inlineStr"/>
       <c r="D71" s="6" t="n"/>
       <c r="E71" s="6" t="n">
         <v>24</v>
@@ -25438,49 +25446,51 @@
         </is>
       </c>
       <c r="G71" s="7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'GRADINITA NR.18' vs 'Venituri din proprietate'; cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'; duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>30.02</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="inlineStr"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="6" t="n">
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'; duplicate of p24 with different values</t>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026; name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -25493,7 +25503,7 @@
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Documentatie Refacere imprejmuire Gradinita nr. 18</t>
         </is>
       </c>
       <c r="D73" s="6" t="n"/>
@@ -25506,334 +25516,318 @@
         </is>
       </c>
       <c r="G73" s="7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Venituri din proprietate'; cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (35%): 'Documentatie Refacere imprejmuire Gradin' vs 'Venituri din proprietate'; duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>30.02</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Documentatie Refacere imprejmuire Gradinita nr. 18</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n">
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026; name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (35%): 'Documentatie Refacere imprejmuire Gradin' vs 'Venituri din proprietate'; duplicate of p24 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="inlineStr"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n">
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="8" t="inlineStr"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'; cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
         <v>24</v>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" s="3" t="n">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="n"/>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="8" t="inlineStr"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n">
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n"/>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="8" t="inlineStr"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
+    <row r="79">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Dcumentatie tehnico-economica pentru construire corp cladire pentru activitati</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
         <v>24</v>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" s="3" t="n">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="4" t="n"/>
-      <c r="C79" s="8" t="inlineStr"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n">
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>didactice la Scoala Duiliu Zamfirescu</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Dcumentatie tehnico-economica pentru construire corp cladire pentru activitati</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
+    <row r="81">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie tehnico-economica -Instalare surse secundare de producere agent termic local la corpurile de scoala principale ale unitatilor de invatamant alimentate din</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
         <v>24</v>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" s="3" t="n">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n"/>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>didactice la Scoala Duiliu Zamfirescu</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n">
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n"/>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>sistemul public de termoficare (20 unitati de invatamant)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Documentatie tehnico-economica -Instalare surse secundare de producere agent termic local la corpurile de scoala principale ale unitatilor de invatamant alimentate din</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
+    <row r="83">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIUL NATIONAL UNIREA</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
         <v>24</v>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" s="3" t="n">
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="n"/>
-      <c r="B83" s="4" t="n"/>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>sistemul public de termoficare (20 unitati de invatamant)</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n">
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n"/>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="8" t="inlineStr"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>COLEGIUL NATIONAL UNIREA</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
+    <row r="85">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Reabilitare, modernizare, extindere si dotare Centru de Stiinte Aplicate</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
         <v>24</v>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" s="3" t="n">
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="n"/>
-      <c r="B85" s="4" t="n"/>
-      <c r="C85" s="8" t="inlineStr"/>
-      <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="n">
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n"/>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>C.N.Unirea</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="5" t="n"/>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Reabilitare, modernizare, extindere si dotare Centru de Stiinte Aplicate</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>24</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F86" s="4" t="inlineStr"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
       <c r="B87" s="4" t="n"/>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>C.N.Unirea</t>
-        </is>
-      </c>
+      <c r="C87" s="8" t="inlineStr"/>
       <c r="D87" s="4" t="n"/>
       <c r="E87" s="4" t="n">
         <v>24</v>
@@ -25848,14 +25842,18 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell 'IⅡI' in column total_2026</t>
+          <t>unparseable cell 'I' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n"/>
       <c r="B88" s="4" t="n"/>
-      <c r="C88" s="8" t="inlineStr"/>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="D88" s="4" t="n"/>
       <c r="E88" s="4" t="n">
         <v>24</v>
@@ -25870,109 +25868,121 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell 'I' in column total_2026</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n"/>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie tehnico-economica Sistematizare verticala C.N.Unirea</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
         <v>24</v>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="8" t="inlineStr"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Documentatie tehnico-economica Sistematizare verticala C.N.Unirea</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>10.02</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>80.02</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="n"/>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="8" t="inlineStr"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n">
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>10.02</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>80.02</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>LICEUL CU PROGRAM SPORTIV</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J92" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'IⅡI' in column total_2026; name mismatch vs nomenclator (44%): 'LICEUL CU PROGRAM SPORTIV' vs 'Cheltuieli salariale in natura'; duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -25987,11 +25997,7 @@
           <t>80.02</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>LICEUL CU PROGRAM SPORTIV</t>
-        </is>
-      </c>
+      <c r="C93" s="6" t="inlineStr"/>
       <c r="D93" s="6" t="n"/>
       <c r="E93" s="6" t="n">
         <v>24</v>
@@ -26002,53 +26008,55 @@
         </is>
       </c>
       <c r="G93" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H93" s="7" t="n"/>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'LICEUL CU PROGRAM SPORTIV' vs 'Cheltuieli salariale in natura'; duplicate of p24 with different values; cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>10.02</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>80.02</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="6" t="n">
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J94" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026; name mismatch vs nomenclator (54%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Cheltuieli salariale in natura'; duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -26065,7 +26073,7 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Statie dedurizare apa</t>
         </is>
       </c>
       <c r="D95" s="6" t="n"/>
@@ -26078,100 +26086,84 @@
         </is>
       </c>
       <c r="G95" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H95" s="7" t="n"/>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (54%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Cheltuieli salariale in natura'; duplicate of p24 with different values; cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (39%): 'Statie dedurizare apa' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>10.02</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>80.02</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Statie dedurizare apa</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n">
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (39%): 'Statie dedurizare apa' vs 'Cheltuieli salariale in natura'</t>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026; name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'; duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n">
+      <c r="A97" s="4" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="8" t="inlineStr"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="J97" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'; duplicate of p24 with different values; cell re-read from image (unverified transcription)</t>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'I' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
       <c r="B98" s="4" t="n"/>
-      <c r="C98" s="8" t="inlineStr"/>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>SCOALA GIMNAZIALA ADRIAN PAUNESCU</t>
+        </is>
+      </c>
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="4" t="n">
         <v>24</v>
@@ -26186,82 +26178,74 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell 'I' in column total_2026</t>
+          <t>unparseable cell 'II' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n"/>
-      <c r="B99" s="4" t="n"/>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>SCOALA GIMNAZIALA ADRIAN PAUNESCU</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n">
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="E99" t="n">
         <v>24</v>
       </c>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="5" t="n"/>
-      <c r="H99" s="5" t="n"/>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>unparseable cell 'II' in column total_2026</t>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="E100" t="n">
+      <c r="A100" s="4" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Reabilitare sistem de incalzire corp cladire Scoala Adrian Paunescu</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n"/>
-      <c r="B101" s="4" t="n"/>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>Reabilitare sistem de incalzire corp cladire Scoala Adrian Paunescu</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>SCOALA GIMNAZIALA ION BASGAN</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>25</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>SCOALA GIMNAZIALA ION BASGAN</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -26279,7 +26263,7 @@
     <row r="103">
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Documentatie realizare grup sanitar destinat persoanelor cu dizabilitati</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -26297,7 +26281,7 @@
     <row r="104">
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Documentatie realizare grup sanitar destinat persoanelor cu dizabilitati</t>
+          <t>SCOALA GIMNAZIALA AL.VLAHUTA</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -26315,7 +26299,7 @@
     <row r="105">
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>SCOALA GIMNAZIALA AL.VLAHUTA</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -26333,7 +26317,7 @@
     <row r="106">
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Sistem de alarmare impotriva efractiei Gradinita nr. 1</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -26351,7 +26335,7 @@
     <row r="107">
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Sistem de alarmare impotriva efractiei Gradinita nr. 1</t>
+          <t>SANATATE</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -26369,7 +26353,7 @@
     <row r="108">
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>SANATATE</t>
+          <t>DIRECTIA DE ASISTENTA SOCIALA</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -26387,7 +26371,7 @@
     <row r="109">
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>DIRECTIA DE ASISTENTA SOCIALA</t>
+          <t>Platforma hidraulica transport persoane Dispensar Sud</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -26405,7 +26389,7 @@
     <row r="110">
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Platforma hidraulica transport persoane Dispensar Sud</t>
+          <t>Implementarea unui sistem de incalzire la Dispensar Sud</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -26423,7 +26407,7 @@
     <row r="111">
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Implementarea unui sistem de incalzire la Dispensar Sud</t>
+          <t>CULTURĂ, RECREERE ŞI RELIGIE</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -26441,7 +26425,7 @@
     <row r="112">
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>CULTURĂ, RECREERE ŞI RELIGIE</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Documentatie tehnico-economica Reabilitare si regenerare zona parc Teatru Documentatie tehnico-economica pentru obtinerea autorizatiei de construire DTAC Reabilitare si regenerare zona parc Teatru DIRECTIA DE DEZVOLTARE SERVICII PUBLICE ALTE CHELTUIELI DE INVESTITII Documentatie tehnico-economica Restaurare si punere in valoare a monumentului istoric de for public Statuia Independentei</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -26449,7 +26433,9 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
+      <c r="H112" s="3" t="n">
+        <v>67.02</v>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -26459,17 +26445,15 @@
     <row r="113">
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Documentatie tehnico-economica Reabilitare si regenerare zona parc Teatru Documentatie tehnico-economica pentru obtinerea autorizatiei de construire DTAC Reabilitare si regenerare zona parc Teatru DIRECTIA DE DEZVOLTARE SERVICII PUBLICE ALTE CHELTUIELI DE INVESTITII Documentatie tehnico-economica Restaurare si punere in valoare a monumentului istoric de for public Statuia Independentei</t>
+          <t>ASIGURĂRI ŞI ASISTENTĂ SOCIALĂ</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n">
-        <v>67.02</v>
-      </c>
+      <c r="H113" s="3" t="n"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -26479,7 +26463,7 @@
     <row r="114">
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ASIGURĂRI ŞI ASISTENTĂ SOCIALĂ</t>
+          <t>68.02 DIRECTIA DE ASISTENTA SOCIALA ALTE CHELTUIELI DE INVESTITII Echipament gatit profesional Elevator electric transfer pacienti capacitate min 200 kg Multifunctional Kyocera Ecosys 3 buc LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -26487,7 +26471,9 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="n"/>
+      <c r="H114" s="3" t="n">
+        <v>68.02</v>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -26497,7 +26483,7 @@
     <row r="115">
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>68.02 DIRECTIA DE ASISTENTA SOCIALA ALTE CHELTUIELI DE INVESTITII Echipament gatit profesional Elevator electric transfer pacienti capacitate min 200 kg Multifunctional Kyocera Ecosys 3 buc LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICĂ</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa II Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa III Sistematizare verticala si modernizare retele utilitati publice in ansamblu rezidential din str.Comisia Centrala. Extindere retea de distributie gaze naturale in cartierul Mandresti Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa IV Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa V Alimentare cu energie electrica statii de pompare ape uzate Sistematizare verticala si racordare la utilitati Locuinte pentru tineri destinate inchirierii , Mun Focsani, calea Munteniei nr.57 Consolidare seismica si cresterea eficientei energetice a imobilului Casa Braileanu ALTE CHELTUIELI DE INVESTITII _PUZ strapungere DN23-Drum acces Statia de Epurare</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -26506,7 +26492,7 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" s="3" t="n"/>
       <c r="H115" s="3" t="n">
-        <v>68.02</v>
+        <v>70.02</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -26517,17 +26503,15 @@
     <row r="116">
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa II Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa III Sistematizare verticala si modernizare retele utilitati publice in ansamblu rezidential din str.Comisia Centrala. Extindere retea de distributie gaze naturale in cartierul Mandresti Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa IV Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa V Alimentare cu energie electrica statii de pompare ape uzate Sistematizare verticala si racordare la utilitati Locuinte pentru tineri destinate inchirierii , Mun Focsani, calea Munteniei nr.57 Consolidare seismica si cresterea eficientei energetice a imobilului Casa Braileanu ALTE CHELTUIELI DE INVESTITII _PUZ strapungere DN23-Drum acces Statia de Epurare</t>
+          <t>CAPITOL/OBIECTIV</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="n">
-        <v>70.02</v>
-      </c>
+      <c r="H116" s="3" t="n"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -26537,7 +26521,7 @@
     <row r="117">
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>CAPITOL/OBIECTIV</t>
+          <t>Expertize, verificari proiecte, studii tehnice, taxe diverse</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -26555,7 +26539,7 @@
     <row r="118">
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Expertize, verificari proiecte, studii tehnice, taxe diverse</t>
+          <t>Documentatie-PUZ -Zona construita protejata (Studii preliminare, studii de</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -26573,7 +26557,7 @@
     <row r="119">
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Documentatie-PUZ -Zona construita protejata (Studii preliminare, studii de</t>
+          <t>specialitate, elaborare PUZ CP si RLU)</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -26591,7 +26575,7 @@
     <row r="120">
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>specialitate, elaborare PUZ CP si RLU)</t>
+          <t>Cazan incalzire blocuri ANL (2 buc)</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -26609,7 +26593,7 @@
     <row r="121">
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Cazan incalzire blocuri ANL (2 buc)</t>
+          <t>Documentatii evaluare vizuala rapida a constructiilor conform Legii 212/2022</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -26627,7 +26611,7 @@
     <row r="122">
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Documentatii evaluare vizuala rapida a constructiilor conform Legii 212/2022</t>
+          <t>Documentatie tehnico-economica pentru proiectul "Regenerare urbana a</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -26645,7 +26629,7 @@
     <row r="123">
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru proiectul "Regenerare urbana a</t>
+          <t>zonei centrale a Municipiului Focsani"</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -26663,7 +26647,7 @@
     <row r="124">
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>zonei centrale a Municipiului Focsani"</t>
+          <t>Documentatie tehnico-economica pentru obtinerea autorizatiei de construire</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -26681,7 +26665,7 @@
     <row r="125">
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru obtinerea autorizatiei de construire</t>
+          <t>"Regenerare urbana a zonei centrale a Municipiului Focsani"</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -26699,7 +26683,7 @@
     <row r="126">
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>"Regenerare urbana a zonei centrale a Municipiului Focsani"</t>
+          <t>_Documentatie tehnico-economica Faza SF pentru proiectul Capacitati de productie energie electrica din surse regenerabile de energie pentru cosumul</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -26717,7 +26701,7 @@
     <row r="127">
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>_Documentatie tehnico-economica Faza SF pentru proiectul Capacitati de productie energie electrica din surse regenerabile de energie pentru cosumul</t>
+          <t>propriu al Municipiului Focsani</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -26735,7 +26719,7 @@
     <row r="128">
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>propriu al Municipiului Focsani</t>
+          <t>Actualizare documentatie tehnico-economica pentru proiectul Consolidarea, restaurarea si dotarea imobilului din Bd. Garii nr. 10, Casa Longinescu-Cod</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -26753,7 +26737,7 @@
     <row r="129">
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Actualizare documentatie tehnico-economica pentru proiectul Consolidarea, restaurarea si dotarea imobilului din Bd. Garii nr. 10, Casa Longinescu-Cod</t>
+          <t>LMI VN-II-m-B-06434</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -26771,7 +26755,7 @@
     <row r="130">
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>LMI VN-II-m-B-06434</t>
+          <t>Stuiu de fundamentare privind necesitatea si oportunitatea concesionarii de</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -26789,7 +26773,7 @@
     <row r="131">
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Stuiu de fundamentare privind necesitatea si oportunitatea concesionarii de</t>
+          <t>servicii si lucrari in vederea Construire centru comercial multifunctional - parcari, spatii de depozitare, spatii de vanzare</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -26807,7 +26791,7 @@
     <row r="132">
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>servicii si lucrari in vederea Construire centru comercial multifunctional - parcari, spatii de depozitare, spatii de vanzare</t>
+          <t>Stuiu de fundamentare privind necesitatea si oportunitatea concesionarii de servicii si lucrari in vederea Construire parcare subterana multietajata str.</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -26825,7 +26809,7 @@
     <row r="133">
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Stuiu de fundamentare privind necesitatea si oportunitatea concesionarii de servicii si lucrari in vederea Construire parcare subterana multietajata str.</t>
+          <t>Dimitrie Cantemir</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -26843,7 +26827,7 @@
     <row r="134">
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Dimitrie Cantemir</t>
+          <t>Documentatie tehnico-economica Infiintare capacitati de stocare energie</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -26861,7 +26845,7 @@
     <row r="135">
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica Infiintare capacitati de stocare energie</t>
+          <t>electrica din surse regenerabile</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -26879,7 +26863,7 @@
     <row r="136">
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>electrica din surse regenerabile</t>
+          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -26897,7 +26881,7 @@
     <row r="137">
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
+          <t>Racord electricitate si apa in sensurile giratorii (E85 Brailei, E85 Cuza Voda,</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -26915,7 +26899,7 @@
     <row r="138">
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Racord electricitate si apa in sensurile giratorii (E85 Brailei, E85 Cuza Voda,</t>
+          <t>str.Marasesti -Bd.Independentei)</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -26933,7 +26917,7 @@
     <row r="139">
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>str.Marasesti -Bd.Independentei)</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -26951,7 +26935,7 @@
     <row r="140">
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Modul Wi-Fi (6 buc)</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -26969,7 +26953,7 @@
     <row r="141">
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Modul Wi-Fi (6 buc)</t>
+          <t>Monitor diagonala 53 inch (4 buc)</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -26987,7 +26971,7 @@
     <row r="142">
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Monitor diagonala 53 inch (4 buc)</t>
+          <t>Videowall pentru 4 monitoare</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -27005,7 +26989,7 @@
     <row r="143">
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Videowall pentru 4 monitoare</t>
+          <t>Volumetrie intrare in oras "Focsani"</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -27023,11 +27007,11 @@
     <row r="144">
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Volumetrie intrare in oras "Focsani"</t>
+          <t>Sistem video -alimentare cu acumulatori (12 buc)</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" s="3" t="n"/>
@@ -27041,7 +27025,7 @@
     <row r="145">
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Sistem video -alimentare cu acumulatori (12 buc)</t>
+          <t>Unitate de monitorizare -camere video (4 buc)</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -27059,7 +27043,7 @@
     <row r="146">
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Unitate de monitorizare -camere video (4 buc)</t>
+          <t>Unitate de alimentare -camere video (4 buc)</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -27077,7 +27061,7 @@
     <row r="147">
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Unitate de alimentare -camere video (4 buc)</t>
+          <t>Sistem de supraveghere video cu 4 camere pentru parc auto</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -27095,7 +27079,7 @@
     <row r="148">
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Sistem de supraveghere video cu 4 camere pentru parc auto</t>
+          <t>Documentatie Alimentare cu apa atelier lacatuserie str. Mihai Eminescu</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -27113,7 +27097,7 @@
     <row r="149">
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Documentatie Alimentare cu apa atelier lacatuserie str. Mihai Eminescu</t>
+          <t>Licenta antivirirus (16 buc)</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -27131,7 +27115,7 @@
     <row r="150">
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Licenta antivirirus (16 buc)</t>
+          <t>Licenta AIMETIS (4 buc)</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -27149,7 +27133,7 @@
     <row r="151">
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Licenta AIMETIS (4 buc)</t>
+          <t>Licenta suport AIMETIS (1 buc)</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -27167,7 +27151,7 @@
     <row r="152">
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Licenta suport AIMETIS (1 buc)</t>
+          <t>Statie de lucru pentru supraveghere video (3 buc)</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -27185,7 +27169,7 @@
     <row r="153">
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Statie de lucru pentru supraveghere video (3 buc)</t>
+          <t>Camera supraveghere video cu panou solar (5 buc)</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -27203,7 +27187,7 @@
     <row r="154">
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Camera supraveghere video cu panou solar (5 buc)</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -27221,7 +27205,7 @@
     <row r="155">
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Server management documente</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -27239,7 +27223,7 @@
     <row r="156">
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Server management documente</t>
+          <t>Licenta Symphony camera Axis cu upgrade 1 an (44 buc)</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -27257,7 +27241,7 @@
     <row r="157">
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Licenta Symphony camera Axis cu upgrade 1 an (44 buc)</t>
+          <t>Licenta Symphony dispozitiv extern cu upgrade 1 an (5 buc)</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -27275,7 +27259,7 @@
     <row r="158">
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Licenta Symphony dispozitiv extern cu upgrade 1 an (5 buc)</t>
+          <t>PROTECTIA MEDIULUI PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Extindere si modernizare sistem de apa si canalizare in judetul Vrancea - Cofinantare proiect POIM et a Il a</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -27283,7 +27267,9 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" s="3" t="n"/>
-      <c r="H158" s="3" t="n"/>
+      <c r="H158" s="3" t="n">
+        <v>74.02</v>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -27293,17 +27279,15 @@
     <row r="159">
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>PROTECTIA MEDIULUI PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Extindere si modernizare sistem de apa si canalizare in judetul Vrancea - Cofinantare proiect POIM et a Il a</t>
+          <t>COMBUSTIBILI ŞI ENERGIE</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" s="3" t="n"/>
-      <c r="H159" s="3" t="n">
-        <v>74.02</v>
-      </c>
+      <c r="H159" s="3" t="n"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -27313,7 +27297,7 @@
     <row r="160">
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>COMBUSTIBILI ŞI ENERGIE</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Documentatie tehnico-economica pentru racordarea la SNT a Centralei Electro Termice (CET) a UAT Focsani, judetul Vrancea TRANSPORTURI PRIMĂRIA MUNICIPIULUI FOCŞANI Refacere infrastructură str.lon Basgan Refacere infrastructura stradala si parcari adiacente strazilor Maior Gh. Pastia, M. Kogalniceanu, D. Cantemir, Cuza Voda - PT8 Refacere infrastructura strazi, sistematizare verticala str. Prof. C. Stere, str. Ecaterina Varga, str. Bujor, str. Agriculturii, str.Muresului,str. Cernei, str.Dogariei, str.Crisana, str.Greva de la Grivita Refacere infrastructura str.Alecu Sihleanu si fundatura, str.Maior G. Sonțu si fundatura, str. Aviatorilor, Aleea Cuza Voda și fundatura Refacere infrastructura strazi, sistematizare verticala str. Fagaras, str. Gh. Potop, str. Ghioceilor, str.Arges, str.Dinicu Golescu, str.Zorilor,P-ta Victoriei Refacere infrastructura strazi, sistematizare verticala str. Viilor si refacere covoare asfaltice carosabil, trotuare, amenajare parcari str. Frunzei, str. Nordului, str Prosperitatii, str. Oborul de Vite, reparatii si asternere covor asfaltic carosabil str. Rovine Refacere infrastructură strazi, sistematizare verticala,parcari, spatii verzi si accese pentru str. N. lorga, str. Oituz (tronson cuprins între str. Marasti și str. D. Zamfirescu), str. Miorita, str.Stefan cel Mare , str.Eroilor, str.Vamii Refacere infrastructura strazi, alei acces auto si parcari zona Bahne, str. Cezar Bolliac(tronson cuprins intre str. Cuza Voda si str. Lupeni), str.Doctor Telemac, str. Rarau, str. Dornei, str. Pictor Grigorescu(tronson cuprins intre str. Al.Vlahuta si str. Panduri), Aleea Caminului, str. Al.Vlahuta, str. Lupeni (tronson cuprins intre str. Cezar Bolliac si Aleea Caminului) Construire drum acces pe teren CF nr. 61771 (MAPN) Reabilitare suprafata carosabila Calea Moldovei - Calea Munteniei</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -27321,7 +27305,9 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" s="3" t="n"/>
-      <c r="H160" s="3" t="n"/>
+      <c r="H160" s="3" t="n">
+        <v>81.02</v>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -27331,17 +27317,15 @@
     <row r="161">
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII Documentatie tehnico-economica pentru racordarea la SNT a Centralei Electro Termice (CET) a UAT Focsani, judetul Vrancea TRANSPORTURI PRIMĂRIA MUNICIPIULUI FOCŞANI Refacere infrastructură str.lon Basgan Refacere infrastructura stradala si parcari adiacente strazilor Maior Gh. Pastia, M. Kogalniceanu, D. Cantemir, Cuza Voda - PT8 Refacere infrastructura strazi, sistematizare verticala str. Prof. C. Stere, str. Ecaterina Varga, str. Bujor, str. Agriculturii, str.Muresului,str. Cernei, str.Dogariei, str.Crisana, str.Greva de la Grivita Refacere infrastructura str.Alecu Sihleanu si fundatura, str.Maior G. Sonțu si fundatura, str. Aviatorilor, Aleea Cuza Voda și fundatura Refacere infrastructura strazi, sistematizare verticala str. Fagaras, str. Gh. Potop, str. Ghioceilor, str.Arges, str.Dinicu Golescu, str.Zorilor,P-ta Victoriei Refacere infrastructura strazi, sistematizare verticala str. Viilor si refacere covoare asfaltice carosabil, trotuare, amenajare parcari str. Frunzei, str. Nordului, str Prosperitatii, str. Oborul de Vite, reparatii si asternere covor asfaltic carosabil str. Rovine Refacere infrastructură strazi, sistematizare verticala,parcari, spatii verzi si accese pentru str. N. lorga, str. Oituz (tronson cuprins între str. Marasti și str. D. Zamfirescu), str. Miorita, str.Stefan cel Mare , str.Eroilor, str.Vamii Refacere infrastructura strazi, alei acces auto si parcari zona Bahne, str. Cezar Bolliac(tronson cuprins intre str. Cuza Voda si str. Lupeni), str.Doctor Telemac, str. Rarau, str. Dornei, str. Pictor Grigorescu(tronson cuprins intre str. Al.Vlahuta si str. Panduri), Aleea Caminului, str. Al.Vlahuta, str. Lupeni (tronson cuprins intre str. Cezar Bolliac si Aleea Caminului) Construire drum acces pe teren CF nr. 61771 (MAPN) Reabilitare suprafata carosabila Calea Moldovei - Calea Munteniei</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" s="3" t="n"/>
-      <c r="H161" s="3" t="n">
-        <v>81.02</v>
-      </c>
+      <c r="H161" s="3" t="n"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -27351,7 +27335,7 @@
     <row r="162">
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Actualizare documentatie tehnico-economica Reabilitare Pasaj pe str. Marasesti (DN 2D km+223) peste magistrala CF 500 Buzau -Marasesti in mun Focsani</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -27367,11 +27351,12 @@
       </c>
     </row>
     <row r="163">
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Actualizare documentatie tehnico-economica Reabilitare Pasaj pe str. Marasesti (DN 2D km+223) peste magistrala CF 500 Buzau -Marasesti in mun Focsani</t>
-        </is>
-      </c>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>79.86</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr"/>
       <c r="E163" t="n">
         <v>30</v>
       </c>
@@ -27385,11 +27370,6 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>79.86</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr"/>
       <c r="E164" t="n">
         <v>30</v>
@@ -27404,55 +27384,59 @@
       </c>
     </row>
     <row r="165">
-      <c r="C165" s="2" t="inlineStr"/>
-      <c r="E165" t="n">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="n"/>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Documentatie PUZ Amenajare cale de acces Cimitir Sudic din Mun Focsani</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="n"/>
+      <c r="E165" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" s="3" t="n"/>
-      <c r="H165" s="3" t="n"/>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>expense_functional</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n"/>
+      <c r="H165" s="7" t="n"/>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (36%): 'Documentatie PUZ Amenajare cale de acces' vs 'Locuinte, servicii si dezvoltare publica'</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>Documentatie PUZ Amenajare cale de acces Cimitir Sudic din Mun Focsani</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n">
+      <c r="C166" s="2" t="inlineStr"/>
+      <c r="E166" t="n">
         <v>30</v>
       </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="n"/>
-      <c r="H166" s="7" t="n"/>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J166" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (36%): 'Documentatie PUZ Amenajare cale de acces' vs 'Locuinte, servicii si dezvoltare publica'</t>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="C167" s="2" t="inlineStr"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Doa e De e de --e ra</t>
+        </is>
+      </c>
       <c r="E167" t="n">
         <v>30</v>
       </c>
@@ -27468,7 +27452,7 @@
     <row r="168">
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Doa e De e de --e ra</t>
+          <t>Actualizare studiu de trafic pentru proiectul Management trafic</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -27484,11 +27468,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Actualizare studiu de trafic pentru proiectul Management trafic</t>
-        </is>
-      </c>
+      <c r="C169" s="2" t="inlineStr"/>
       <c r="E169" t="n">
         <v>30</v>
       </c>
@@ -27502,7 +27482,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="C170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Actualizare studiu de trafic pentru proiectul Modernizare transport public</t>
+        </is>
+      </c>
       <c r="E170" t="n">
         <v>30</v>
       </c>
@@ -27516,11 +27500,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Actualizare studiu de trafic pentru proiectul Modernizare transport public</t>
-        </is>
-      </c>
+      <c r="C171" s="2" t="inlineStr"/>
       <c r="E171" t="n">
         <v>30</v>
       </c>
@@ -27562,7 +27542,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="C174" s="2" t="inlineStr"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E174" t="n">
         <v>30</v>
       </c>
@@ -27576,11 +27560,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C175" s="2" t="inlineStr"/>
       <c r="E175" t="n">
         <v>30</v>
       </c>
@@ -27594,7 +27574,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="C176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Sistem de semaforizare intersectie Kaufland str. Marasesti</t>
+        </is>
+      </c>
       <c r="E176" t="n">
         <v>30</v>
       </c>
@@ -27608,11 +27592,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Sistem de semaforizare intersectie Kaufland str. Marasesti</t>
-        </is>
-      </c>
+      <c r="C177" s="2" t="inlineStr"/>
       <c r="E177" t="n">
         <v>30</v>
       </c>
@@ -27626,7 +27606,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="C178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Sistem de semaforizare trecere de pietoni str. 1 Decembrie 1918</t>
+        </is>
+      </c>
       <c r="E178" t="n">
         <v>30</v>
       </c>
@@ -27640,11 +27624,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Sistem de semaforizare trecere de pietoni str. 1 Decembrie 1918</t>
-        </is>
-      </c>
+      <c r="C179" s="2" t="inlineStr"/>
       <c r="E179" t="n">
         <v>30</v>
       </c>
@@ -27658,16 +27638,40 @@
       </c>
     </row>
     <row r="180">
-      <c r="C180" s="2" t="inlineStr"/>
-      <c r="E180" t="n">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>10.02</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>Placa vibro-compactoare</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="n"/>
+      <c r="E180" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" s="3" t="n"/>
-      <c r="H180" s="3" t="n"/>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="n"/>
+      <c r="H180" s="7" t="n"/>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (30%): 'Placa vibro-compactoare' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -27682,11 +27686,7 @@
           <t>70.02</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>Placa vibro-compactoare</t>
-        </is>
-      </c>
+      <c r="C181" s="6" t="inlineStr"/>
       <c r="D181" s="6" t="n"/>
       <c r="E181" s="6" t="n">
         <v>30</v>
@@ -27704,40 +27704,6 @@
         </is>
       </c>
       <c r="J181" s="6" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (30%): 'Placa vibro-compactoare' vs 'Cheltuieli salariale in natura'</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr"/>
-      <c r="D182" s="6" t="n"/>
-      <c r="E182" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G182" s="7" t="n"/>
-      <c r="H182" s="7" t="n"/>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="J182" s="6" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
@@ -28310,7 +28276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28356,12 +28322,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -28379,19 +28345,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 03.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>03.02 total_2026: parent 310,00 != sum(children) 2,03 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -28409,19 +28375,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 16.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>16.02 total_2026: parent 12,59 != sum(children) 90,51 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -28439,19 +28405,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 35.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>35.02 total_2026: parent 4,09 != sum(children) 967,12 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -28469,19 +28435,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total_2026: parent 69,26 != sum(children) 169,16 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -28499,14 +28465,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>42.02 total_2026: parent 11,75 != sum(children) 261,50 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -28515,28 +28481,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (55%): 'SUBVENTII PENTRU INVESTITII' vs 'Subventii de la bugetul de stat'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -28545,28 +28506,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.69</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2014-202' vs 'Subvenţii de la bugetul de stat către bu'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -28575,28 +28531,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (51%): 'Sume BS cofinantare proiecte UE 2021-202' vs 'Subvenţii de la bugetul de stat necesare'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -28605,131 +28556,141 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.65</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Finanţarea Programului Naţional de Dezvo'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>45.02</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p5: 0 cells recovered</t>
+          <t>name mismatch vs nomenclator (50%): 'SUME DE PRIMIT DE LA UE 2021-2027' vs 'Sume primite de la UE/alti donatori în c'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p6: 1 cells recovered</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p15: 0 cells recovered</t>
+          <t>unparseable cell '2,115 1,000' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>54.02.07</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p24: 8 cells recovered</t>
+          <t>name mismatch vs nomenclator (43%): '*Fond de rezerva bugetara *Fond pt.garan' vs 'Fond pentru garantarea împrumuturilor ex'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>03.02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>03.02 total_2026: parent 310,00 != sum(children) 2,03 (1 children)</t>
+          <t>name mismatch vs nomenclator (25%): 'Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
@@ -28745,11 +28706,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -28759,122 +28720,112 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16.02 total_2026: parent 12,59 != sum(children) 90,51 (3 children)</t>
+          <t>61.02 total_2026: parent 9,99 != sum(children) 180,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35.02</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.02 total_2026: parent 4,09 != sum(children) 967,12 (2 children)</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>61.02.05</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11.02 total_2026: parent 69,26 != sum(children) 169,16 (3 children)</t>
+          <t>name mismatch vs nomenclator (52%): '*Protectia civila' vs 'Protectie civila si protectia contra inc'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.02 total_2026: parent 11,75 != sum(children) 261,50 (2 children)</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (55%): 'SUBVENTII PENTRU INVESTITII' vs 'Subventii de la bugetul de stat'</t>
+          <t>66.02 total_2026: parent 11,99 != sum(children) 11,96 (1 children)</t>
         </is>
       </c>
     </row>
@@ -28890,23 +28841,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.02.69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2014-202' vs 'Subvenţii de la bugetul de stat către bu'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -28915,16 +28866,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.02.93</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (51%): 'Sume BS cofinantare proiecte UE 2021-202' vs 'Subvenţii de la bugetul de stat necesare'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -28940,41 +28891,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.02.65</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Finanţarea Programului Naţional de Dezvo'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'SUME DE PRIMIT DE LA UE 2021-2027' vs 'Sume primite de la UE/alti donatori în c'</t>
+          <t>68.02 total_2026: parent 70,32 != sum(children) 34,32 (2 children)</t>
         </is>
       </c>
     </row>
@@ -28990,7 +28946,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -28999,7 +28955,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29015,7 +28971,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -29024,7 +28980,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>unparseable cell '2,115 1,000' in column total_2026</t>
+          <t>unparseable cell '45,997 6,750' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -29040,71 +28996,71 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.02.07</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (43%): '*Fond de rezerva bugetara *Fond pt.garan' vs 'Fond pentru garantarea împrumuturilor ex'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
+          <t>74.02 total_2026: parent 15,78 != sum(children) 450,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 9,99 != sum(children) 180,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29120,16 +29076,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (38%): 'operatiuni financiare' vs 'TITLUL XX RAMBURSARI DE CREDITE'</t>
         </is>
       </c>
     </row>
@@ -29145,16 +29101,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>61.02.05</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (52%): '*Protectia civila' vs 'Protectie civila si protectia contra inc'</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29170,46 +29126,41 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 11,99 != sum(children) 11,96 (1 children)</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29225,16 +29176,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
         </is>
       </c>
     </row>
@@ -29244,77 +29195,72 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>51</t>
+        <v>8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>unparseable cell 'VENITURI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>71</t>
+        <v>8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>unparseable cell 'Venituri operationale' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 70,32 != sum(children) 34,32 (2 children)</t>
+          <t>name mismatch vs nomenclator (34%): 'proiecte Consiliul Local al Tinerilor' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -29330,46 +29276,41 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (35%): 'Cap 80.02 Alte servicii economice genera' vs 'Împrumuturi pentru persoane cu statut de'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>70.02.10</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (32%): 'investitii' vs 'TITLUL VII ALTE TRANSFERURI'</t>
         </is>
       </c>
     </row>
@@ -29385,71 +29326,66 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): 'alte drepturi sociale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 15,78 != sum(children) 450,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (44%): 'varsaminte la bugetul de stat aferent pe' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>71</t>
+        <v>11</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>unparseable cell "000'6" in column total_2026</t>
         </is>
       </c>
     </row>
@@ -29465,16 +29401,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'operatiuni financiare' vs 'TITLUL XX RAMBURSARI DE CREDITE'</t>
+          <t>name mismatch vs nomenclator (13%): '(materiale dendrologice, ingrasaminte, u' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
@@ -29490,16 +29426,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (34%): 'iluminat public' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
@@ -29515,16 +29451,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
+          <t>name mismatch vs nomenclator (35%): 'materiale intretinere iluminat' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
@@ -29540,16 +29476,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (38%): 'finantare complementara scoala' vs 'Reparatii curente'</t>
         </is>
       </c>
     </row>
@@ -29565,16 +29501,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
+          <t>name mismatch vs nomenclator (44%): 'finantare complementara gradinita' vs 'Reparatii curente'</t>
         </is>
       </c>
     </row>
@@ -29584,47 +29520,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>14</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20.02</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>unparseable cell 'VENITURI' in column total_2026</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>est2027</t>
+        <v>15</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>unparseable cell 'Venituri operationale' in column est2027</t>
+          <t>name mismatch vs nomenclator (32%): 'finantare de baza' vs 'Locuinte, servicii si dezvoltare publica'</t>
         </is>
       </c>
     </row>
@@ -29640,66 +29576,66 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'proiecte Consiliul Local al Tinerilor' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (34%): 'gradinita finantare de baza' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>80.02</t>
+        <v>15</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Cap 80.02 Alte servicii economice genera' vs 'Împrumuturi pentru persoane cu statut de'</t>
+          <t>unparseable cell '1,042.00 642.00' in column total</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>55</t>
+        <v>15</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'investitii' vs 'TITLUL VII ALTE TRANSFERURI'</t>
+          <t>unparseable cell '1,195.00 854.00' in column total</t>
         </is>
       </c>
     </row>
@@ -29715,41 +29651,41 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'alte drepturi sociale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (36%): 'finantare complementara' vs 'Actiuni generale economice, comerciale s'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>15</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'varsaminte la bugetul de stat aferent pe' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell '1,009.00 469.00' in column total</t>
         </is>
       </c>
     </row>
@@ -29765,141 +29701,141 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>unparseable cell "000'6" in column total_2026</t>
+          <t>unparseable cell '826.00 761.00' in column total</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>31.02</t>
+        <v>17</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (13%): '(materiale dendrologice, ingrasaminte, u' vs 'Venituri din dobanzi'</t>
+          <t>unparseable cell '一' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>35.02</t>
+        <v>17</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'iluminat public' vs 'Amenzi, penalitati si confiscari'</t>
+          <t>unparseable cell 'A' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>35.02</t>
+        <v>17</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'materiale intretinere iluminat' vs 'Amenzi, penalitati si confiscari'</t>
+          <t>unparseable cell 'B' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>20.02</t>
+        <v>17</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'finantare complementara scoala' vs 'Reparatii curente'</t>
+          <t>unparseable cell 'II' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>20.02</t>
+        <v>17</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'finantare complementara gradinita' vs 'Reparatii curente'</t>
+          <t>unparseable cell 'ⅢII' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -29909,47 +29845,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>20.02</t>
+        <v>17</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>duplicate of p14 with different values</t>
+          <t>unparseable cell 'a' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>15</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>70.02</t>
+        <v>17</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'finantare de baza' vs 'Locuinte, servicii si dezvoltare publica'</t>
+          <t>unparseable cell 'b' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -29965,41 +29901,41 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>51.02.07</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'gradinita finantare de baza' vs 'Taxe pe servicii specifice'</t>
+          <t>name mismatch vs nomenclator (29%): 'AUTORITĂTI PUBLICE' vs 'Finanţarea studiilor de fezabilitate afe'</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>19</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>unparseable cell '1,042.00 642.00' in column total</t>
+          <t>name mismatch vs nomenclator (16%): '-r a t a n 1 2027' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
         </is>
       </c>
     </row>
@@ -30009,22 +29945,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>19</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>unparseable cell '1,195.00 854.00' in column total</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -30040,16 +29976,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>70.02.07</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'finantare complementara' vs 'Actiuni generale economice, comerciale s'</t>
+          <t>name mismatch vs nomenclator (46%): 'LOCUINTE ŞI DEZVOLTARE PUBLICÃ, LOCUINTE' vs 'Alimantare cu gaze naturale in localitat'</t>
         </is>
       </c>
     </row>
@@ -30059,22 +29995,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>19</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>unparseable cell '1,009.00 469.00' in column total</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -30084,22 +30020,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>15</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>19</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>unparseable cell '826.00 761.00' in column total</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -30109,22 +30045,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>19</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>unparseable cell '一' in column total_2026</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -30134,47 +30070,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>19</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>unparseable cell 'A' in column total_2026</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>17</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>24</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>unparseable cell 'B' in column total_2026</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -30190,7 +30126,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -30199,32 +30135,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>unparseable cell 'II' in column total_2026</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>24</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅢII' in column total_2026</t>
+          <t>name mismatch vs nomenclator (43%): 'Sistem de avertizare audio-video si pano' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -30234,22 +30170,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>24</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>unparseable cell 'a' in column total_2026</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -30265,7 +30201,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -30274,32 +30210,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>unparseable cell 'b' in column total_2026</t>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>19</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>51.02.07</t>
+        <v>24</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'AUTORITĂTI PUBLICE' vs 'Finanţarea studiilor de fezabilitate afe'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30315,16 +30251,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (16%): '-r a t a n 1 2027' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -30334,22 +30270,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>19</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>60</t>
+        <v>24</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>unparseable cell 'II' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30365,23 +30301,23 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>70.02.07</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'LOCUINTE ŞI DEZVOLTARE PUBLICÃ, LOCUINTE' vs 'Alimantare cu gaze naturale in localitat'</t>
+          <t>name mismatch vs nomenclator (46%): 'GRADINITA NR.18' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -30390,16 +30326,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -30415,16 +30351,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -30434,29 +30370,29 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>19</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>60</t>
+        <v>24</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -30465,16 +30401,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -30494,19 +30430,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>name mismatch vs nomenclator (35%): 'Documentatie Refacere imprejmuire Gradin' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -30519,12 +30455,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (43%): 'Sistem de avertizare audio-video si pano' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -30534,34 +30470,34 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>24</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>12.02</t>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -30569,17 +30505,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
         </is>
       </c>
     </row>
@@ -30604,29 +30535,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>unparseable cell 'IⅡI' in column total_2026</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>24</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>24.02</t>
-        </is>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -30634,79 +30560,74 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>24</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>24</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'GRADINITA NR.18' vs 'Venituri din proprietate'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>24</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -30714,32 +30635,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>24</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30749,69 +30670,64 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>24</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>unparseable cell 'I' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>24</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Venituri din proprietate'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>24</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>total_2026</t>
@@ -30819,7 +30735,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30839,12 +30755,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Documentatie Refacere imprejmuire Gradin' vs 'Venituri din proprietate'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -30854,22 +30770,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>24</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>30.02</t>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>unparseable cell 'IⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -30889,24 +30805,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Venituri din proprietate'</t>
+          <t>name mismatch vs nomenclator (44%): 'LICEUL CU PROGRAM SPORTIV' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -30914,42 +30830,37 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>24</v>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -30981,25 +30892,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>24</v>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (54%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -31009,47 +30920,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>24</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>24</v>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>name mismatch vs nomenclator (39%): 'Statie dedurizare apa' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -31074,32 +30985,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>unparseable cell 'IⅡI' in column total_2026</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>24</v>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>unparseable cell 'I' in column total_2026</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -31109,22 +31020,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>24</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>10.02</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -31149,64 +31060,64 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
+          <t>unparseable cell 'I' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>24</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>10.02</t>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
+          <t>unparseable cell 'II' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>24</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>10.02</t>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'LICEUL CU PROGRAM SPORTIV' vs 'Cheltuieli salariale in natura'</t>
+          <t>unparseable cell 'ⅡI' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -31215,46 +31126,41 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>name mismatch vs nomenclator (36%): 'Documentatie PUZ Amenajare cale de acces' vs 'Locuinte, servicii si dezvoltare publica'</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>10.02</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (30%): 'Placa vibro-compactoare' vs 'Cheltuieli salariale in natura'</t>
         </is>
       </c>
     </row>
@@ -31270,7 +31176,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -31278,341 +31184,6 @@
         </is>
       </c>
       <c r="F114" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>24</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (54%): 'ALTE CHELTUIELI DE INVESTITII' vs 'Cheltuieli salariale in natura'</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>24</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>duplicate of p24 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>24</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>24</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (39%): 'Statie dedurizare apa' vs 'Cheltuieli salariale in natura'</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>24</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>24</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>duplicate of p24 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>24</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>24</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>unparseable cell 'I' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>24</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>unparseable cell 'II' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>24</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>unparseable cell 'ⅡI' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>30</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (36%): 'Documentatie PUZ Amenajare cale de acces' vs 'Locuinte, servicii si dezvoltare publica'</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>30</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (30%): 'Placa vibro-compactoare' vs 'Cheltuieli salariale in natura'</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>30</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (0%): '' vs 'Cheltuieli salariale in natura'</t>
         </is>
@@ -31629,7 +31200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -31651,106 +31222,276 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>245</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>176</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>71.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— BUGETUL GENERAL CENTRALIZAT AL MUNICIPIULUI FOCSANI PE ANUL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>general, pag. 1-19, 623 linii</t>
-        </is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>— BUGETUL LOCAL I - C</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>local, pag. 20-30, 181 linii</t>
-        </is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4d4df771e01847d72b86711f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6564117f742e92ef18443ff0eb166013f511b2b26e8c0ad79d8783549bc3f0de</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Modele LLM folosite</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>gemini-3.6-flash</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>— BUGETUL GENERAL CENTRALIZAT AL MUNICIPIULUI FOCSANI PE ANUL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>general, pag. 1-19, 623 linii</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>— BUGETUL LOCAL I - C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>local, pag. 20-30, 180 linii</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL CREDITELOR INTERNE I - C</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>credite_interne, pag. 31-33, 28 linii</t>
         </is>
